--- a/sources/jin_step4.xlsx
+++ b/sources/jin_step4.xlsx
@@ -423,8 +423,8 @@
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">

--- a/sources/jin_step4.xlsx
+++ b/sources/jin_step4.xlsx
@@ -785,6 +785,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
@@ -817,6 +822,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
@@ -854,6 +864,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
@@ -891,6 +906,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
@@ -928,6 +948,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
@@ -965,6 +990,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>cda82971-a307-467e-ad05-57768181324c</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>cda82971-a307-467e-ad05-57768181324c</t>
@@ -1012,6 +1042,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
@@ -1054,6 +1089,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
@@ -1094,6 +1134,11 @@
       <c r="L16" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>67cda8df-b3c2-4b5d-83b0-595685761a80</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -6632,6 +6677,11 @@
           <t>hhhLmmlhhmm</t>
         </is>
       </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
@@ -6659,6 +6709,11 @@
           <t>hhhLmmlhhmL</t>
         </is>
       </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
@@ -6686,6 +6741,11 @@
           <t>hhhLmmlhhlh</t>
         </is>
       </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
@@ -6713,6 +6773,11 @@
           <t>hhhhmmL h m m</t>
         </is>
       </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
@@ -6740,6 +6805,11 @@
           <t>hhhhmmLLm!</t>
         </is>
       </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
@@ -6767,6 +6837,11 @@
           <t>hhmhlhhmmm</t>
         </is>
       </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
@@ -6794,6 +6869,11 @@
           <t>hhmmlmLm!</t>
         </is>
       </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
@@ -6821,6 +6901,11 @@
           <t>hhmhlhhmm</t>
         </is>
       </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
@@ -6848,6 +6933,11 @@
           <t>hhmhlhhmL</t>
         </is>
       </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
@@ -6873,6 +6963,11 @@
       <c r="J138" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>73b74b43-c81d-45eb-972e-07cbd1c76456</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">

--- a/sources/jin_step4.xlsx
+++ b/sources/jin_step4.xlsx
@@ -807,6 +807,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -847,6 +852,11 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>– 2,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
